--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.55261316234841</v>
+        <v>2.364799638881617</v>
       </c>
       <c r="D2" t="n">
-        <v>15.26239258328311</v>
+        <v>2.480138794783505</v>
       </c>
       <c r="E2" t="n">
-        <v>14.40405477684969</v>
+        <v>2.340658901238074</v>
       </c>
       <c r="F2" t="n">
-        <v>13.87442879376814</v>
+        <v>2.254594678987322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.49627266055101</v>
+        <v>6.743144307339539</v>
       </c>
       <c r="D3" t="n">
-        <v>33.73992762365359</v>
+        <v>5.482738238843709</v>
       </c>
       <c r="E3" t="n">
-        <v>14.40405477684969</v>
+        <v>2.340658901238074</v>
       </c>
       <c r="F3" t="n">
-        <v>13.87442879376814</v>
+        <v>2.254594678987322</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.00896763770364</v>
+        <v>4.713957241126842</v>
       </c>
       <c r="D4" t="n">
-        <v>28.82983807844528</v>
+        <v>4.684848687747357</v>
       </c>
       <c r="E4" t="n">
-        <v>14.40405477684969</v>
+        <v>2.340658901238074</v>
       </c>
       <c r="F4" t="n">
-        <v>13.87442879376814</v>
+        <v>2.254594678987322</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.14271624332546</v>
+        <v>3.110691389540388</v>
       </c>
       <c r="D5" t="n">
-        <v>18.81810404861821</v>
+        <v>3.057941907900459</v>
       </c>
       <c r="E5" t="n">
-        <v>14.40405477684969</v>
+        <v>2.340658901238074</v>
       </c>
       <c r="F5" t="n">
-        <v>13.87442879376814</v>
+        <v>2.254594678987322</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.54791862961601</v>
+        <v>9.514036777312603</v>
       </c>
       <c r="D6" t="n">
-        <v>57.99137228837701</v>
+        <v>9.423597996861265</v>
       </c>
       <c r="E6" t="n">
-        <v>14.40405477684969</v>
+        <v>2.340658901238074</v>
       </c>
       <c r="F6" t="n">
-        <v>13.87442879376814</v>
+        <v>2.254594678987322</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.45519023281668</v>
+        <v>5.923968412832711</v>
       </c>
       <c r="D7" t="n">
-        <v>35.96537177790355</v>
+        <v>5.844372913909327</v>
       </c>
       <c r="E7" t="n">
-        <v>14.40405477684969</v>
+        <v>2.340658901238074</v>
       </c>
       <c r="F7" t="n">
-        <v>13.87442879376814</v>
+        <v>2.254594678987322</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.1797293200222</v>
+        <v>7.666706014503608</v>
       </c>
       <c r="D8" t="n">
-        <v>46.63902258790443</v>
+        <v>7.57884117053447</v>
       </c>
       <c r="E8" t="n">
-        <v>14.40405477684969</v>
+        <v>2.340658901238074</v>
       </c>
       <c r="F8" t="n">
-        <v>13.87442879376814</v>
+        <v>2.254594678987322</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
